--- a/public/uploads/files/sample_category_Bulk_upload.xlsx
+++ b/public/uploads/files/sample_category_Bulk_upload.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>item_code</t>
   </si>
@@ -30,16 +30,28 @@
     <t>HIACRASG318PCC2SS</t>
   </si>
   <si>
-    <t>BONBROCKERZ238PROFUS</t>
-  </si>
-  <si>
-    <t>NONBTUNECHARGEBK</t>
-  </si>
-  <si>
-    <t>Air Conditioner</t>
-  </si>
-  <si>
-    <t>Split Ac</t>
+    <t>Large Appliance</t>
+  </si>
+  <si>
+    <t>Split AC</t>
+  </si>
+  <si>
+    <t>SALEUA43F5500FUXXL</t>
+  </si>
+  <si>
+    <t>Televisions</t>
+  </si>
+  <si>
+    <t>FULL HD</t>
+  </si>
+  <si>
+    <t>HPSWSTYLE183BTCAL</t>
+  </si>
+  <si>
+    <t>Gadgets</t>
+  </si>
+  <si>
+    <t>WEARABLES</t>
   </si>
 </sst>
 </file>
@@ -404,32 +416,32 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
